--- a/DCZ/touch_rect_log_20260608_154703.xlsx
+++ b/DCZ/touch_rect_log_20260608_154703.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\logs\294\DCZ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EtoHayato\Desktop\git_repository\294\DCZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF5662B-9AE0-437D-AC13-85322CF09F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE693989-3C29-4D5B-9075-EC13BA5EEB91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5880" yWindow="825" windowWidth="25785" windowHeight="15375" activeTab="1" xr2:uid="{DC5E61C2-CB2A-49F0-AF3D-9DEDC863C581}"/>
+    <workbookView xWindow="18195" yWindow="1905" windowWidth="25455" windowHeight="14670" activeTab="1" xr2:uid="{DC5E61C2-CB2A-49F0-AF3D-9DEDC863C581}"/>
   </bookViews>
   <sheets>
     <sheet name="touch_rect_log_20260608_154703" sheetId="1" r:id="rId1"/>
@@ -4153,7 +4153,7 @@
             </a:r>
             <a:r>
               <a:rPr lang="en-US" altLang="ja-JP" baseline="0"/>
-              <a:t> 0.1 ug/kg</a:t>
+              <a:t> 1 ug/kg</a:t>
             </a:r>
             <a:endParaRPr lang="ja-JP" altLang="en-US"/>
           </a:p>
@@ -5734,15 +5734,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>23812</xdr:colOff>
+      <xdr:colOff>23811</xdr:colOff>
       <xdr:row>228</xdr:row>
-      <xdr:rowOff>176212</xdr:rowOff>
+      <xdr:rowOff>176211</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>481012</xdr:colOff>
-      <xdr:row>240</xdr:row>
-      <xdr:rowOff>61912</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>352424</xdr:colOff>
+      <xdr:row>250</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
